--- a/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>26430</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39025</t>
+          <t>38050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37573</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56061</t>
+          <t>57226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72820</t>
+          <t>73504</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>68,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>18412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>30032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>13356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>24400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35013</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51772</t>
+          <t>50607</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>46,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107405</t>
+          <t>107170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133462</t>
+          <t>134637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132278</t>
+          <t>133390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162964</t>
+          <t>164486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249576</t>
+          <t>249363</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289936</t>
+          <t>288152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176855</t>
+          <t>175680</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202912</t>
+          <t>203147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190672</t>
+          <t>189150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221358</t>
+          <t>220246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>374017</t>
+          <t>375801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>414377</t>
+          <t>414590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39195</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57496</t>
+          <t>57653</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>36464</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54742</t>
+          <t>53717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80823</t>
+          <t>80405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105365</t>
+          <t>105773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79085</t>
+          <t>78928</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97386</t>
+          <t>97668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68800</t>
+          <t>69825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87018</t>
+          <t>87078</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154758</t>
+          <t>154350</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>179300</t>
+          <t>179718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,09%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182877</t>
+          <t>181145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>216941</t>
+          <t>217000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>208567</t>
+          <t>208778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243856</t>
+          <t>245146</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>401501</t>
+          <t>399580</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>451997</t>
+          <t>453282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>286418</t>
+          <t>286359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320482</t>
+          <t>322214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284693</t>
+          <t>283403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>319982</t>
+          <t>319771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>579911</t>
+          <t>578626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>630407</t>
+          <t>632328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27556</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39637</t>
+          <t>39678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31912</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44269</t>
+          <t>44313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62977</t>
+          <t>63765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81064</t>
+          <t>80775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>27671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36510</t>
+          <t>36799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54597</t>
+          <t>53809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125310</t>
+          <t>124178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153606</t>
+          <t>153156</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147023</t>
+          <t>146757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177424</t>
+          <t>178494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281378</t>
+          <t>282050</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322941</t>
+          <t>324515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151047</t>
+          <t>151497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179343</t>
+          <t>180475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162369</t>
+          <t>161299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>192770</t>
+          <t>193036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>321505</t>
+          <t>319931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>363068</t>
+          <t>362396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,23%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40033</t>
+          <t>39825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57331</t>
+          <t>57322</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48124</t>
+          <t>47353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66797</t>
+          <t>67920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93223</t>
+          <t>93515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119494</t>
+          <t>119290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59496</t>
+          <t>59505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76794</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70101</t>
+          <t>68978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88774</t>
+          <t>89545</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134231</t>
+          <t>134435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>160502</t>
+          <t>160210</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205564</t>
+          <t>204644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>239769</t>
+          <t>239956</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>239227</t>
+          <t>240217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276099</t>
+          <t>278303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>454290</t>
+          <t>454476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>509320</t>
+          <t>506927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237196</t>
+          <t>237009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271401</t>
+          <t>272321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262682</t>
+          <t>260478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299554</t>
+          <t>298564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>506426</t>
+          <t>508819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>561456</t>
+          <t>561270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17893</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27690</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19531</t>
+          <t>19076</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30811</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39674</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55175</t>
+          <t>55283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,17%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>13190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22748</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20426</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31706</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36703</t>
+          <t>36595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52204</t>
+          <t>51636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,2%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131624</t>
+          <t>131534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>160767</t>
+          <t>160631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140461</t>
+          <t>139244</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>170692</t>
+          <t>172302</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>277646</t>
+          <t>280669</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322709</t>
+          <t>322461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,26%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>187955</t>
+          <t>188091</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>217098</t>
+          <t>217188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209174</t>
+          <t>207564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239405</t>
+          <t>240622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>405879</t>
+          <t>406127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>450942</t>
+          <t>447919</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44973</t>
+          <t>45583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64010</t>
+          <t>64085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44917</t>
+          <t>44562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63175</t>
+          <t>64220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95398</t>
+          <t>96091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123207</t>
+          <t>121355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>43,98%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72017</t>
+          <t>71942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91054</t>
+          <t>90444</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>75710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95013</t>
+          <t>95368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152750</t>
+          <t>154602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180559</t>
+          <t>179866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205187</t>
+          <t>206228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245939</t>
+          <t>241106</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216460</t>
+          <t>214222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254440</t>
+          <t>253416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>429534</t>
+          <t>430455</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>483422</t>
+          <t>483498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>279451</t>
+          <t>284284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320203</t>
+          <t>319162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>316593</t>
+          <t>317617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354573</t>
+          <t>356811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>613001</t>
+          <t>612925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666889</t>
+          <t>665968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,74%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44656</t>
+          <t>45324</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52749</t>
+          <t>52820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50264</t>
+          <t>50364</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58440</t>
+          <t>58565</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97938</t>
+          <t>97555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109649</t>
+          <t>109377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>9354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>422890</t>
+          <t>423368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>442064</t>
+          <t>442001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>472691</t>
+          <t>473407</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>494543</t>
+          <t>496160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>905655</t>
+          <t>906297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>933228</t>
+          <t>933095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>18509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37620</t>
+          <t>37142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43928</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43901</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71474</t>
+          <t>70832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147274</t>
+          <t>147261</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177829</t>
+          <t>177603</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182716</t>
+          <t>182722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>326101</t>
+          <t>326212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331905</t>
+          <t>331843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>621760</t>
+          <t>622325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>641313</t>
+          <t>641289</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>708305</t>
+          <t>709120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>732249</t>
+          <t>732502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1338446</t>
+          <t>1336962</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1367718</t>
+          <t>1368909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23425</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42978</t>
+          <t>42413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53667</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58992</t>
+          <t>57801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88264</t>
+          <t>89748</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32599</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27369</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38329</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>63,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>53,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32548</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26430</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38050</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25789</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>38297</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>32599</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>26971</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38015</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>63,46%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57226</t>
+          <t>56941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73504</t>
+          <t>73708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18772</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13042</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24002</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>46,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>23914</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18412</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30032</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18165</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>30673</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>42,35%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>53,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18772</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13356</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24400</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34329</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50607</t>
+          <t>50892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>148084</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>134609</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>164133</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>38,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>120084</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>107170</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>134637</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>106734</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>134089</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>38,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>43,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>148084</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>133390</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>164486</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>41,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249363</t>
+          <t>247497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288152</t>
+          <t>289004</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>205552</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>189503</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>219027</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>61,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>190233</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>175680</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>203147</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>176228</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>203583</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>61,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>56,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>205552</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>189150</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>220246</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>58,13%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>375801</t>
+          <t>374949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>414590</t>
+          <t>416456</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45550</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>36526</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>54883</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>47514</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38913</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57653</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37852</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>56810</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>45550</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>36464</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>53717</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,87%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80405</t>
+          <t>81669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105773</t>
+          <t>105529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77992</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>68659</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>87016</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>63,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>55,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>89067</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78928</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>97668</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79771</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>98729</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>65,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>71,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77992</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>69825</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87078</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>63,13%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154350</t>
+          <t>154594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>179718</t>
+          <t>178454</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>208384</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>245623</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,43%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>200145</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>181145</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>217000</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>181684</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>218077</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>39,76%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>226233</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>208778</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>245146</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>399580</t>
+          <t>400649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>453282</t>
+          <t>450187</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>302316</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>282926</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>320165</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>450</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>303214</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>286359</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>322214</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>285282</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>321675</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>60,24%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>302316</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>283403</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>319771</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>57,2%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>578626</t>
+          <t>581721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632328</t>
+          <t>631259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38355</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31218</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44717</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>34242</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27813</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39678</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>27812</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39905</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>50,13%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38355</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31712</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>44313</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>61,77%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>51,07%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63765</t>
+          <t>64264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80775</t>
+          <t>81574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23735</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17373</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30872</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21242</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15806</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27671</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15579</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27672</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>49,87%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23735</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17777</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30378</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,23%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>28,63%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>48,93%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>63</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36799</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53809</t>
+          <t>53310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>163352</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>147934</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>177836</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>52,34%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>139588</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>124178</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>153156</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>125707</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>155318</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>45,82%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>50,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>163352</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>146757</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>178494</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>48,07%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>282050</t>
+          <t>283912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324515</t>
+          <t>324760</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>176441</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>161957</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>191859</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>47,66%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>56,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>165065</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>151497</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>180475</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>149335</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>178946</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>54,18%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>176441</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>161299</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>193036</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>319931</t>
+          <t>319686</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>362396</t>
+          <t>360534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,94%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>57366</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48063</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>67625</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>49,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>48563</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39825</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57322</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40376</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>57187</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>41,57%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>57366</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>47353</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>67920</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,9%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93515</t>
+          <t>93419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119290</t>
+          <t>119487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>79532</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69273</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88835</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>50,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68264</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>59505</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77002</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>59640</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76451</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>58,43%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>65,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>79532</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>68978</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>89545</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>58,1%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134435</t>
+          <t>134238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>160210</t>
+          <t>160306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>238688</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>276489</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>51,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>320</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>222394</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>204644</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>239956</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>205485</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>239569</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>46,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>42,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>259073</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>240217</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>278303</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>48,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>454476</t>
+          <t>455074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>506927</t>
+          <t>505661</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,78%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>279708</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>262292</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>300093</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>55,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>254571</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>237009</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>272321</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>237396</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>271480</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>49,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>57,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>279708</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>260478</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>298564</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>508819</t>
+          <t>510085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>561270</t>
+          <t>560672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25228</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19517</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31404</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>22761</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17417</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27451</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17668</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>27704</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>56,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,86%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25228</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19076</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>30930</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>40236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55283</t>
+          <t>55589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26009</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19833</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31720</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>61,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17880</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13190</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23224</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12937</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22973</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26009</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>20307</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32161</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36595</t>
+          <t>36289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51636</t>
+          <t>51642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>155436</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>141402</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>171342</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>40,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>145643</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>131534</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>160631</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>130299</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>159876</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>41,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>37,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>46,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>155436</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>139244</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>172302</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>40,92%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280669</t>
+          <t>279528</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322461</t>
+          <t>324381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>224430</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>208524</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>238464</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>59,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>62,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>203079</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>188091</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>217188</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>188846</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>218423</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>58,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>62,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>224430</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>207564</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>240622</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>59,08%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>406127</t>
+          <t>404207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447919</t>
+          <t>449060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53955</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45076</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>63523</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>38,56%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>54269</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>45583</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64085</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45385</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>63518</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>39,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>53955</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>44562</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>64220</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>38,56%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96091</t>
+          <t>95589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121355</t>
+          <t>121723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85975</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76407</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94854</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>61,44%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>54,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>81758</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>71942</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90444</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>72509</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>90642</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>60,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>52,89%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>85975</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>75710</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95368</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>61,44%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154602</t>
+          <t>154234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>179866</t>
+          <t>180368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,36%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>216293</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>255101</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>37,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>44,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>222674</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>206228</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>241106</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>204609</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>239933</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>42,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>234618</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>214222</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>253416</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>430455</t>
+          <t>431014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>483498</t>
+          <t>485340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>336415</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>315932</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>354740</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>55,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>62,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>302716</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>284284</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>319162</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>285457</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>320781</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>57,62%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>336415</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>317617</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>356811</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>612925</t>
+          <t>611083</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>665968</t>
+          <t>665409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,69%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50362</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45634</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53445</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>80,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>49848</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45324</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>52820</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>82,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>55138</t>
+          <t>42028</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50364</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58565</t>
+          <t>44695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>104985</t>
+          <t>92390</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97555</t>
+          <t>85823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109377</t>
+          <t>96670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6370</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4830</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9354</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19127</t>
+          <t>17667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>447597</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>435845</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>455529</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>94,1%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>91,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>603</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>433402</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>423368</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>442001</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>94,11%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>91,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>486020</t>
+          <t>405661</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>473407</t>
+          <t>397056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>496160</t>
+          <t>413827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>919421</t>
+          <t>853258</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>906297</t>
+          <t>838764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>933095</t>
+          <t>865940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28081</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20149</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39833</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>27108</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18509</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37142</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>26787</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>18621</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43212</t>
+          <t>35392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>57708</t>
+          <t>54868</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44034</t>
+          <t>42186</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70832</t>
+          <t>69362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,74 +6218,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>166238</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>162387</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>167705</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>96,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>149001</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>147261</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>149293</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>147775</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>181012</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>177603</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>182722</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>462</t>
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>330013</t>
+          <t>315531</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>326212</t>
+          <t>312051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331843</t>
+          <t>317149</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2181</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6032</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2290</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2201</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5746</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>664197</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>651951</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>673502</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>93,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>632250</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>622325</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>641289</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>93,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>722169</t>
+          <t>596982</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>709120</t>
+          <t>586050</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>732502</t>
+          <t>605882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1354419</t>
+          <t>1261179</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1336962</t>
+          <t>1244765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1368909</t>
+          <t>1273714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36632</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27327</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48878</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>32488</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>23449</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42413</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29470</t>
+          <t>23300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52852</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>68832</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57801</t>
+          <t>56297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89748</t>
+          <t>85246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
